--- a/data/trans_bre/P16A_n_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 11,89</t>
+          <t>-0,11; 11,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 10,43</t>
+          <t>-3,2; 10,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 5,94</t>
+          <t>-6,45; 5,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 8,64</t>
+          <t>-2,18; 9,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 83,32</t>
+          <t>-0,75; 84,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 57,89</t>
+          <t>-14,35; 57,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 31,52</t>
+          <t>-25,75; 30,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 33,85</t>
+          <t>-7,25; 36,71</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 15,3</t>
+          <t>3,55; 14,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 14,05</t>
+          <t>1,12; 14,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 8,32</t>
+          <t>-4,51; 8,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 11,14</t>
+          <t>-0,4; 11,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 129,59</t>
+          <t>19,11; 134,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 80,23</t>
+          <t>4,51; 79,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 41,17</t>
+          <t>-17,8; 43,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 46,41</t>
+          <t>-1,38; 46,29</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 17,51</t>
+          <t>2,99; 18,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 14,36</t>
+          <t>-0,06; 14,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 21,72</t>
+          <t>4,98; 22,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,33; 48,64</t>
+          <t>17,24; 49,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 115,4</t>
+          <t>15,88; 117,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 52,1</t>
+          <t>-0,3; 50,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 91,35</t>
+          <t>18,3; 94,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,15; 607,71</t>
+          <t>49,16; 588,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 8,08</t>
+          <t>0,25; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 8,95</t>
+          <t>-0,23; 9,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 7,04</t>
+          <t>-1,49; 6,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 39,22</t>
+          <t>2,28; 38,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 39,98</t>
+          <t>1,58; 43,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 33,56</t>
+          <t>-0,71; 34,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 30,07</t>
+          <t>-5,55; 29,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 117,45</t>
+          <t>6,44; 116,21</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 16,78</t>
+          <t>5,17; 16,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,75; 26,01</t>
+          <t>14,44; 25,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 20,52</t>
+          <t>10,53; 20,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 17,42</t>
+          <t>-1,34; 18,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,13; 113,51</t>
+          <t>23,96; 109,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,46; 112,03</t>
+          <t>47,61; 110,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,91; 87,89</t>
+          <t>36,99; 89,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 56,43</t>
+          <t>-0,44; 60,59</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,64; 34,21</t>
+          <t>27,07; 34,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,89; 44,51</t>
+          <t>35,8; 44,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,69; 40,65</t>
+          <t>31,75; 40,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,98; 39,96</t>
+          <t>26,53; 39,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>324,36; 993,45</t>
+          <t>331,0; 1042,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>285,3; 885,76</t>
+          <t>306,18; 931,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>305,37; 917,69</t>
+          <t>312,43; 937,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>160,65; 762,82</t>
+          <t>160,63; 799,72</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,3; 14,44</t>
+          <t>10,39; 14,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,06</t>
+          <t>12,61; 17,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,05</t>
+          <t>9,43; 14,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,76; 26,52</t>
+          <t>9,87; 25,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,6; 87,62</t>
+          <t>56,01; 87,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,57; 71,35</t>
+          <t>47,72; 72,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,22; 64,58</t>
+          <t>38,84; 64,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,76; 115,87</t>
+          <t>31,75; 103,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 11,92</t>
+          <t>-0,05; 11,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 10,39</t>
+          <t>-2,28; 10,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 5,88</t>
+          <t>-6,18; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 9,03</t>
+          <t>-1,87; 7,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 84,05</t>
+          <t>-1,02; 79,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 57,45</t>
+          <t>-9,27; 61,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 30,05</t>
+          <t>-25,06; 35,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 36,71</t>
+          <t>-6,33; 31,81</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 14,72</t>
+          <t>3,49; 14,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 14,36</t>
+          <t>0,78; 14,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 8,35</t>
+          <t>-4,55; 8,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 11,15</t>
+          <t>-0,08; 10,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,11; 134,43</t>
+          <t>19,74; 130,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 79,95</t>
+          <t>3,1; 77,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 43,08</t>
+          <t>-17,51; 44,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 46,29</t>
+          <t>-0,05; 44,99</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,98</t>
+          <t>19,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>146,13%</t>
+          <t>59,86%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 18,34</t>
+          <t>2,7; 17,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 14,37</t>
+          <t>-0,46; 14,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 22,26</t>
+          <t>4,35; 22,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,24; 49,87</t>
+          <t>11,93; 26,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,88; 117,51</t>
+          <t>12,68; 111,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 50,49</t>
+          <t>-0,28; 50,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 94,57</t>
+          <t>15,57; 93,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,16; 588,98</t>
+          <t>35,13; 94,09</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,55</t>
+          <t>0,73; 8,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 9,26</t>
+          <t>0,45; 9,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 6,91</t>
+          <t>-1,81; 6,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 38,05</t>
+          <t>-0,27; 7,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 43,5</t>
+          <t>3,06; 41,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 34,5</t>
+          <t>1,16; 34,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 29,93</t>
+          <t>-6,86; 26,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 116,21</t>
+          <t>-0,95; 23,49</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,55</t>
+          <t>17,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 16,21</t>
+          <t>6,01; 17,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 25,54</t>
+          <t>15,0; 25,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,53; 20,39</t>
+          <t>10,39; 20,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 18,24</t>
+          <t>11,59; 21,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,96; 109,69</t>
+          <t>28,7; 115,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,61; 110,31</t>
+          <t>50,92; 112,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,99; 89,39</t>
+          <t>37,65; 89,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 60,59</t>
+          <t>33,24; 79,49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33,95</t>
+          <t>32,13</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>353,5%</t>
+          <t>311,44%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,07; 34,39</t>
+          <t>27,05; 34,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,8; 44,71</t>
+          <t>35,3; 44,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,75; 40,97</t>
+          <t>32,34; 40,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,53; 39,71</t>
+          <t>24,73; 37,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>331,0; 1042,58</t>
+          <t>309,75; 997,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>306,18; 931,62</t>
+          <t>282,41; 856,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>312,43; 937,96</t>
+          <t>305,89; 942,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>160,63; 799,72</t>
+          <t>142,63; 625,91</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,48</t>
+          <t>10,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 14,37</t>
+          <t>10,21; 14,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,61; 17,3</t>
+          <t>12,56; 17,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,43; 14,13</t>
+          <t>9,75; 14,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 25,91</t>
+          <t>8,55; 12,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,01; 87,25</t>
+          <t>55,29; 87,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,72; 72,38</t>
+          <t>47,33; 70,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,84; 64,26</t>
+          <t>41,0; 64,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,75; 103,62</t>
+          <t>27,6; 44,28</t>
         </is>
       </c>
     </row>
